--- a/AIGC和生成式大模型/AIGC和生成式大模型汇总.xlsx
+++ b/AIGC和生成式大模型/AIGC和生成式大模型汇总.xlsx
@@ -8,14 +8,548 @@
   </bookViews>
   <sheets>
     <sheet name="AIGC综述" sheetId="2" r:id="rId1"/>
-    <sheet name="论文列表" sheetId="4" r:id="rId2"/>
+    <sheet name="VLM论文列表" sheetId="4" r:id="rId2"/>
+    <sheet name="LLM论文列表" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
+  <si>
+    <r>
+      <t>diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>VQGAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>基本上就是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>版的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>VQGAN
+VQGAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>VQVAE+GAN+Perception Loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>VQVAE+DDPM+Perception Loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+VQGAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>都是一批人的工作，也算是系出同源了。不过如果要严谨的说，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>本身确实没什么</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Adversarial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>很多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>计算部分包含对抗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>loss
+VQGAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>VQVAE+GAN+auto regressive+perceptual loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>是把自回归换成了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>diffusion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stable diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>diffusion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stable diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>模型的改进。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>）输入输出均为低维图片向量（而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>直接使用原始图片），这使得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>stable diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>更快。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>模型一般都是直接生成图片，不会有中间生成低维向量的过程，需要更大计算量，在计算速度和资源利用上都比不过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> stable diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>具体而言，就是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Unet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>网络和采样器算法所实现的。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>目前，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>作图引擎主要有五个。最稳定、可用性最好的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Midjourney</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Stable Diffusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans CJK SC Regular"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">
+- Firefly
+- DALL-E2
+- OpenJourney
+- Midjourney
+- Stable Diffusion</t>
+    </r>
+  </si>
   <si>
     <t>Paper</t>
   </si>
@@ -41,39 +575,1106 @@
     <t>补充说明</t>
   </si>
   <si>
+    <t>CLIP: Learning Transferable Visual Models From Natural Language Supervision</t>
+  </si>
+  <si>
+    <t>CLIP(Contrastive Language-Image Pre-Training)；本质是ConVIRT的简化版</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <r>
+      <t>连接文本和图像，达到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>zero shot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果。计算图像与文本向量之间的相似程度，将图片用文本描述出来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>即</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>token)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从互联网上搜集了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亿对（图像，文本）的数据集，用于训练</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CLIP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，然后取得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SOTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的图像表征。预训练完之后，在下游任务上，可以通过用自然语言（文本）匹配视觉（图像）从而实现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>zero-shot transfer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个不同类型的下游</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>任务上进行了基准测试。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+ConVIRT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）对来训练模型，其有一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>image encoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>text encoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，训练目标是让两路的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>representation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尽可能得一致（对偶地最大化表征的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>agreement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loss是最大化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个正确编码图像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标题对之间的余弦相似度，并同时最小化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> N 2 - N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个不正确编码图像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标题对之间的余弦相似度。</t>
+    </r>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Tokenization是计算机理解单词的方式。人类可以读懂单词，但是计算机只能读懂数字。所以这也是为什么文本提示词首先要转为单词。
+Tokenizer只能将其在训练过程中见到过的单词进行分词。例如，假设CLIP模型里有“dream”与“beach”单词，但是没有“dreambeach”单词。Tokenizer会将“dreambeach”分成2个单词“dream”与“beach”。所以，1个单词并非代表1个token，而是有可能进一步进行拆分。
+另一个细节是：空格也是token的一部分。例如，短语 "dream beach" 产生了两个token "dream" 和 "[space]beach"。这些标记与 "dreambeach" 产生的标记不同，后者是 "dream" 和 "beach"（beach 前没有空格）。</t>
+  </si>
+  <si>
+    <r>
+      <t>AIGC</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CV</t>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>领域</t>
+    </r>
+  </si>
+  <si>
+    <t>Hierarchical Text-Conditional Image Generation with CLIP Latents</t>
+  </si>
+  <si>
+    <r>
+      <t>DALL-E2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；未开源；无论文；这轮AIGC（或者视觉领域大模型）的起点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月初，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所开创的模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DALL-E 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发布，这在图像生成和处理领域树立了新的标杆，也可以视为这轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AIGC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（或者视觉领域大模型）的起点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整体架构非常简单。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）将文本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> prompt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入到经过训练以将</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> prompt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>映射到表征空间的文本编码器中。即</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CLIP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模型。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）称为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>先验模型”（diffusion prior）将文本编码映射到相应的图像编码，该图像编码捕获文本编码中包含的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> prompt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的语义信息。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）图像解码模型随机生成图像，该图像是该语义信息的视觉表现。使用的是Diffusion架构，具体是使用GLIDE。</t>
+    </r>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <r>
+      <t>stable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>disffusion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；开源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+  </si>
+  <si>
+    <t>本质是大杂烩，官方直接提供了web端。</t>
+  </si>
+  <si>
+    <t>Midjourney</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <r>
+      <t>只能在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Discord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平台上使用</t>
+    </r>
+  </si>
+  <si>
+    <t>OpenJourney</t>
+  </si>
+  <si>
+    <t>Adobe</t>
+  </si>
+  <si>
+    <t>Firefly</t>
+  </si>
+  <si>
+    <t>imagen</t>
+  </si>
+  <si>
+    <t>Sora</t>
+  </si>
+  <si>
+    <r>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+  </si>
+  <si>
+    <t>文字生成视频</t>
+  </si>
+  <si>
+    <t>openai</t>
+  </si>
+  <si>
+    <t>DALL-E3</t>
+  </si>
+  <si>
+    <t>Stable Diffusion XL</t>
+  </si>
+  <si>
+    <t>Imagen 2</t>
+  </si>
+  <si>
+    <r>
+      <t>dino</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>领域</t>
-    </r>
-  </si>
-  <si>
-    <t>Midjourney</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>stable</t>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系列</t>
+    </r>
+  </si>
+  <si>
+    <t>Grounding DINO: Marrying DINO with Grounded Pre-Training for Open-Set Object Detection</t>
+  </si>
+  <si>
+    <r>
+      <t>Grounding DINO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；根据文字提示检测任意目标；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>github</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开源，还有很多应用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>腾讯；清华大学人工智能研究所；国际数字经济学会（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>IDEA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）；香港科技大学；香港中文大学；微软研究院</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>继</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CLIP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打破文字和图像之间的壁垒、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DINO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提高了目标检测精度的上限之后，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Grounding DINO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结合了这俩的优点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原文图很简洁明确。输入是图文对，输出是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>box/scores/entity property of text</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（多组框和词组）。该算法是一个双编码，单解码的框架，其中，编码器包含图像编码器（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SwinTransformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和文本编码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(bert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等）两个，解码器包含一个交叉模态解码模块。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+DETR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的变种。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SAM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更慢，本地要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Grounding DINO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DINO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>扩展到开放集物体检测，使其能够检测给定文本作为查询的任意对象。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DINO-v2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>跟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>grounding dino</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>没啥关系，甚至出发点也不一样，完全两个团队开发的。</t>
+    </r>
+  </si>
+  <si>
+    <t>Grounding DINO+SAM可以实现很多视觉任务</t>
+  </si>
+  <si>
+    <r>
+      <t>DINO:</t>
     </r>
     <r>
       <rPr>
@@ -89,17 +1690,7 @@
         <rFont val="Nimbus Roman No9 L"/>
         <charset val="134"/>
       </rPr>
-      <t>disffusion</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Stability</t>
+      <t>DETR</t>
     </r>
     <r>
       <rPr>
@@ -115,82 +1706,139 @@
         <rFont val="Nimbus Roman No9 L"/>
         <charset val="134"/>
       </rPr>
-      <t>AI</t>
-    </r>
-  </si>
-  <si>
-    <t>DALL-E2</t>
-  </si>
-  <si>
-    <t>OpenAI</t>
-  </si>
-  <si>
-    <t>OpenJourney</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">通过 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PhotoShop</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 使用</t>
-    </r>
-  </si>
-  <si>
-    <t>Adobe</t>
-  </si>
-  <si>
-    <t>Firefly</t>
-  </si>
-  <si>
-    <t>imagen</t>
-  </si>
-  <si>
-    <t>Grounding DINO</t>
-  </si>
-  <si>
-    <r>
-      <t>根据文字提示检测任意目标。继</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CLIP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打破文字和图像之间的壁垒、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
+      <t>with</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Improved</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DeNoising</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Anchor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Boxes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>End-to-End</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Detection</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>DINO</t>
     </r>
     <r>
@@ -199,26 +1847,23 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>提高了目标检测精度的上限之后，Grounding DINO的又一力作。
-DETR的变种。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DINO:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>github</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开源；基于</t>
     </r>
     <r>
       <rPr>
@@ -234,202 +1879,11 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>with</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Improved</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DeNoising</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Anchor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Boxes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>for</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>End-to-End</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Object</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Detection</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DINO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>github</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开源；基于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DETR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
       <t>；自监督方法</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>香港科技大学；清华大学人工智能研究所；国际数字经济学会（</t>
     </r>
     <r>
@@ -451,12 +1905,8 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
-        <charset val="134"/>
-      </rPr>
-      <t>通过使用标准</t>
+      <t>ViT架构。使用对比学习方法，模型学习从图像检索任务中有用的数据中识别相似和不相似的示例。然而，DINO 放弃了负采样对的通常做法，而是选择了全局自注意力机制。
+通过使用标准</t>
     </r>
     <r>
       <rPr>
@@ -469,7 +1919,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>直接预测教师网络的输出来简化自监督训练。</t>
@@ -481,7 +1931,23 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-1.Contrastive</t>
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Contrastive</t>
     </r>
     <r>
       <rPr>
@@ -578,7 +2044,23 @@
         <rFont val="Nimbus Roman No9 L"/>
         <charset val="134"/>
       </rPr>
-      <t>2.Mix</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Mix</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +2141,23 @@
         <rFont val="Nimbus Roman No9 L"/>
         <charset val="134"/>
       </rPr>
-      <t>3.Look</t>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Look</t>
     </r>
     <r>
       <rPr>
@@ -703,21 +2201,21 @@
     </r>
   </si>
   <si>
+    <t>注意，实现时，增加了一个额外的可学习的token，用来聚合整个embeddings的信息，命名为[CLS]。
+所有patch的这组token和[CLS]这个token一起被送到标准Transformers网络。
+使用CAM（Class Activation Mapping）或者Grad-CAM可以可视化ViT的输出。</t>
+  </si>
+  <si>
     <t>DINOv2: Learning Robust Visual Features without Supervision</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
       <t>DINOv2</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Droid Sans Fallback"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>；一种无监督学习的预训练方法</t>
@@ -725,11 +2223,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
       <t>Mate AI</t>
     </r>
     <r>
@@ -743,11 +2236,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
       <t>DINO</t>
     </r>
     <r>
@@ -788,7 +2276,23 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>的后续工作，其得到的特征适合密集预测任务。</t>
+      <t>的后续工作，其得到的特征适合密集预测任务（所谓密集预测是相对于全局预测的，分类任务就是典型的全局预测；而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>dense prediction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和segment就是典型的密集预测）。</t>
     </r>
     <r>
       <rPr>
@@ -951,14 +2455,26 @@
       </rPr>
       <t>。</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Nimbus Roman No9 L"/>
-        <charset val="134"/>
-      </rPr>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进行了模型蒸馏，使用更快。</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>"</t>
     </r>
     <r>
@@ -983,8 +2499,24 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>问题
-这些</t>
+      <t>问题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这些</t>
     </r>
     <r>
       <rPr>
@@ -1180,6 +2712,42 @@
       </rPr>
       <t>。</t>
     </r>
+  </si>
+  <si>
+    <t>DETR</t>
+  </si>
+  <si>
+    <t>GLIP</t>
+  </si>
+  <si>
+    <r>
+      <t>SAM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系列</t>
+    </r>
+  </si>
+  <si>
+    <t>Segment Anything</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>Mate</t>
+  </si>
+  <si>
+    <t>见《大模型》文件夹</t>
+  </si>
+  <si>
+    <t>SAMed: Customized Segment Anything Model for Medical Image Segmentation</t>
   </si>
 </sst>
 </file>
@@ -1187,14 +2755,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\/m\/d;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\/m\/d;@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1221,7 +2789,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <charset val="0"/>
     </font>
@@ -1246,12 +2814,33 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Nimbus Roman No9 L"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Droid Sans Fallback"/>
+      <name val="Nimbus Roman No9 L"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Nimbus Roman No9 L"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1266,17 +2855,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1289,10 +2871,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1304,45 +2886,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1357,7 +2902,15 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1371,16 +2924,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1388,10 +2977,17 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1402,11 +2998,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1424,7 +3020,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1442,7 +3038,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,115 +3176,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1574,31 +3194,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1609,7 +3205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1634,49 +3230,25 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1711,26 +3283,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1743,6 +3306,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1751,10 +3334,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1763,137 +3346,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1906,7 +3489,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,7 +3501,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1942,7 +3525,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1951,25 +3534,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2296,34 +3894,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B10:C27"/>
+  <dimension ref="B4:C27"/>
   <sheetFormatPr defaultColWidth="11.2636363636364" defaultRowHeight="15.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.6363636363636" style="23"/>
-    <col min="2" max="2" width="47.4" style="23"/>
-    <col min="3" max="3" width="58.0727272727273" style="23"/>
-    <col min="4" max="4" width="73.4363636363636" style="23"/>
-    <col min="5" max="5" width="64.3909090909091" style="23"/>
-    <col min="6" max="16384" width="11.2636363636364" style="24"/>
+    <col min="1" max="1" width="11.6363636363636" style="28"/>
+    <col min="2" max="2" width="47.4" style="28"/>
+    <col min="3" max="3" width="58.0727272727273" style="28"/>
+    <col min="4" max="4" width="73.4363636363636" style="28"/>
+    <col min="5" max="5" width="64.3909090909091" style="28"/>
+    <col min="6" max="16384" width="11.2636363636364" style="29"/>
   </cols>
   <sheetData>
+    <row r="4" ht="124" spans="2:3">
+      <c r="B4" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="108" spans="2:3">
+      <c r="B5" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="108.5" spans="2:2">
+      <c r="B7" s="30" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="25"/>
+      <c r="B10" s="30"/>
     </row>
     <row r="13" spans="2:2">
-      <c r="B13" s="25"/>
+      <c r="B13" s="30"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="25"/>
+      <c r="B17" s="30"/>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="25"/>
+      <c r="B20" s="30"/>
     </row>
     <row r="25" spans="3:3">
-      <c r="C25" s="25"/>
+      <c r="C25" s="30"/>
     </row>
     <row r="27" spans="3:3">
-      <c r="C27" s="25"/>
+      <c r="C27" s="30"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2336,7 +3955,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2350,34 +3969,34 @@
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" spans="1:9">
+    <row r="1" ht="15.5" spans="1:9">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:9">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -2386,10 +4005,788 @@
       <c r="F2" s="12"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
-    </row>
-    <row r="3" ht="15.5" spans="1:8">
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" ht="185.5" spans="1:9">
+      <c r="A3" s="18"/>
+      <c r="B3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="16">
+        <v>44253</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="15.5" spans="1:9">
+      <c r="A4" s="18"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" ht="15.5" spans="1:9">
+      <c r="A5" s="18"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:9">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="30.5" spans="1:9">
+      <c r="A7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" ht="154.5" spans="1:9">
+      <c r="A8" s="18"/>
+      <c r="B8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16">
+        <v>44664</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" ht="15.5" spans="1:9">
+      <c r="A9" s="18"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" ht="15.5" spans="1:9">
+      <c r="A10" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="16">
+        <v>44774</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" ht="15.5" spans="1:9">
+      <c r="A11" s="18"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" ht="15.5" spans="1:9">
+      <c r="A12" s="18"/>
+      <c r="B12" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" ht="15.5" spans="1:9">
+      <c r="A13" s="18"/>
+      <c r="B13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" ht="15.5" spans="1:9">
+      <c r="A14" s="18"/>
+      <c r="B14" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" ht="15.5" spans="1:9">
+      <c r="A15" s="18"/>
+      <c r="B15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" ht="15.5" spans="1:9">
+      <c r="A16" s="18"/>
+      <c r="B16" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="20"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" ht="15.5" spans="1:9">
+      <c r="A17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" ht="15.5" spans="1:9">
+      <c r="A18" s="22"/>
+      <c r="B18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" ht="15.5" spans="1:9">
+      <c r="A19" s="22"/>
+      <c r="B19" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" ht="15.5" spans="1:9">
+      <c r="A20" s="22"/>
+      <c r="B20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" ht="15.5" spans="1:9">
+      <c r="A21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" ht="15.5" spans="1:9">
+      <c r="A22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" ht="15.5" spans="1:9">
+      <c r="A23" s="22"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:9">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" s="3" customFormat="1" ht="30.5" spans="1:9">
+      <c r="A25" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" ht="155" spans="1:9">
+      <c r="A26" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="16">
+        <v>45005</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" ht="15.5" spans="1:9">
+      <c r="A27" s="22"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" ht="169" spans="1:9">
+      <c r="A28" s="18"/>
+      <c r="B28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="16">
+        <v>44753</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" ht="15.5" spans="1:9">
+      <c r="A29" s="18"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" ht="107" spans="1:9">
+      <c r="A30" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="16">
+        <v>45324</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" ht="15.5" spans="1:9">
+      <c r="A31" s="18"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32" ht="15.5" spans="1:9">
+      <c r="A32" s="18"/>
+      <c r="B32" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33" ht="15.5" spans="1:9">
+      <c r="A33" s="18"/>
+      <c r="B33" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" ht="15.5" spans="1:9">
+      <c r="A34" s="18"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" ht="15.5" spans="1:9">
+      <c r="A35" s="18"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:9">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="12"/>
+    </row>
+    <row r="37" s="19" customFormat="1" ht="30.5" spans="1:8">
+      <c r="A37" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" s="19" customFormat="1" ht="15.5" spans="1:8">
+      <c r="A38" s="26"/>
+      <c r="B38" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="24">
+        <v>45021</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" s="19" customFormat="1" ht="15.5" spans="1:8">
+      <c r="A39" s="26"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+    </row>
+    <row r="40" ht="46.5" spans="1:9">
+      <c r="A40" s="18"/>
+      <c r="B40" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="27"/>
+      <c r="I40" s="15"/>
+    </row>
+    <row r="41" ht="15.5" spans="1:9">
+      <c r="A41" s="18"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="15"/>
+    </row>
+    <row r="42" ht="15.5" spans="1:9">
+      <c r="A42" s="18"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="15"/>
+    </row>
+    <row r="43" ht="15.5" spans="1:9">
+      <c r="A43" s="18"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="15"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="18"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="15"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="18"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="15"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:9">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="12"/>
+    </row>
+    <row r="47" ht="15.5" spans="1:9">
+      <c r="A47" s="18"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="15"/>
+    </row>
+    <row r="48" ht="15.5" spans="1:9">
+      <c r="A48" s="18"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="15"/>
+    </row>
+    <row r="49" ht="15.5" spans="1:9">
+      <c r="A49" s="18"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="15"/>
+    </row>
+    <row r="50" ht="15.5" spans="1:9">
+      <c r="A50" s="18"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="15"/>
+    </row>
+    <row r="51" ht="15.5" spans="1:9">
+      <c r="A51" s="18"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="15"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="18"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="15"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="18"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="15"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="18"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.509027777777778" footer="0.509027777777778"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="32.0818181818182" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.2" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.5909090909091" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.7" style="3" customWidth="1"/>
+    <col min="6" max="6" width="70.7" style="3" customWidth="1"/>
+    <col min="7" max="8" width="9" style="5"/>
+    <col min="9" max="9" width="61.3090909090909" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.5" spans="1:9">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:9">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" ht="30.5" spans="1:9">
       <c r="A3" s="14" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="16"/>
@@ -2398,8 +4795,9 @@
       <c r="F3" s="15"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="18"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16"/>
@@ -2408,315 +4806,106 @@
       <c r="F4" s="15"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
-    </row>
-    <row r="5" ht="15.5" spans="1:8">
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="18"/>
-      <c r="B5" s="19" t="s">
-        <v>9</v>
-      </c>
+      <c r="B5" s="15"/>
       <c r="C5" s="16"/>
       <c r="D5" s="15"/>
-      <c r="E5" s="19" t="s">
-        <v>10</v>
-      </c>
+      <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-    </row>
-    <row r="6" ht="15.5" spans="1:8">
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
+      <c r="B6" s="15"/>
       <c r="C6" s="16"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="19" t="s">
-        <v>12</v>
-      </c>
+      <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
-    </row>
-    <row r="7" ht="15.5" spans="1:8">
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="18"/>
-      <c r="B7" s="19" t="s">
-        <v>13</v>
-      </c>
+      <c r="B7" s="15"/>
       <c r="C7" s="16"/>
       <c r="D7" s="15"/>
-      <c r="E7" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="E7" s="15"/>
       <c r="F7" s="15"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
-    </row>
-    <row r="8" ht="30.5" spans="1:8">
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="18"/>
-      <c r="B8" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="B8" s="15"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>17</v>
-      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
-    </row>
-    <row r="9" ht="15.5" spans="1:8">
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
-        <v>18</v>
-      </c>
+      <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-    </row>
-    <row r="10" ht="15.5" spans="1:8">
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
-        <v>19</v>
-      </c>
+      <c r="B10" s="15"/>
       <c r="C10" s="16"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-    </row>
-    <row r="11" ht="45.5" spans="1:8">
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="18"/>
-      <c r="B11" s="15" t="s">
-        <v>20</v>
-      </c>
+      <c r="B11" s="15"/>
       <c r="C11" s="16"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="15" t="s">
-        <v>21</v>
-      </c>
+      <c r="F11" s="15"/>
       <c r="G11" s="17"/>
       <c r="H11" s="17"/>
-    </row>
-    <row r="12" ht="124" spans="1:8">
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="18"/>
-      <c r="B12" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="16">
-        <v>44753</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>25</v>
-      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
-    </row>
-    <row r="13" ht="15.5" spans="1:8">
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="19"/>
+      <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="19"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
-    </row>
-    <row r="14" ht="107" spans="1:9">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="16">
-        <v>45324</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="18"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="18"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="18"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="18"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="18"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="18"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="18"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="18"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="18"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="18"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="18"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="18"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="18"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="18"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="18"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="18"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="I13" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.509027777777778" footer="0.509027777777778"/>
